--- a/PM.xlsx
+++ b/PM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{679DF1DE-F5F1-4FD6-930D-963B6EB6C783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF0B32EC-DC02-4CD7-B2EA-0E39EA792729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{237199C3-ED65-4E36-BE9B-24893DBB0CE2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" xr2:uid="{237199C3-ED65-4E36-BE9B-24893DBB0CE2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -161,7 +161,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="269">
   <si>
     <t>Philipp Morris</t>
   </si>
@@ -965,6 +965,9 @@
   </si>
   <si>
     <t>FY25</t>
+  </si>
+  <si>
+    <t>https://web.quartr.com/search/all?articleId=bb65609e-1f13-4724-88ed-673487c6a60b&amp;documentType=article</t>
   </si>
 </sst>
 </file>
@@ -1454,6 +1457,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="172" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1466,11 +1474,6 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1824,7 +1827,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DB38893-A6D1-4F9C-9C30-8A2037A3C6D2}">
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="2" customWidth="1"/>
@@ -1871,7 +1874,7 @@
       <c r="K4" s="6">
         <v>1556.6795790000001</v>
       </c>
-      <c r="L4" s="90" t="s">
+      <c r="L4" s="86" t="s">
         <v>258</v>
       </c>
     </row>
@@ -1919,7 +1922,7 @@
       <c r="K6" s="6">
         <v>4872</v>
       </c>
-      <c r="L6" s="90" t="s">
+      <c r="L6" s="86" t="s">
         <v>258</v>
       </c>
     </row>
@@ -1944,7 +1947,7 @@
         <f>168+3533+45134</f>
         <v>48835</v>
       </c>
-      <c r="L7" s="90" t="s">
+      <c r="L7" s="86" t="s">
         <v>258</v>
       </c>
     </row>
@@ -2021,6 +2024,11 @@
     <row r="18" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>245</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B19" s="2" t="s">
+        <v>268</v>
       </c>
     </row>
   </sheetData>
@@ -2109,7 +2117,7 @@
       <c r="V2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="W2" s="90" t="s">
+      <c r="W2" s="86" t="s">
         <v>267</v>
       </c>
     </row>
@@ -2254,7 +2262,7 @@
       <c r="V4" s="8">
         <v>0.23499999999999999</v>
       </c>
-      <c r="W4" s="91">
+      <c r="W4" s="87">
         <v>0.23400000000000001</v>
       </c>
     </row>
@@ -2326,7 +2334,7 @@
       <c r="V5" s="8">
         <v>5.1999999999999998E-2</v>
       </c>
-      <c r="W5" s="91">
+      <c r="W5" s="87">
         <v>5.8000000000000003E-2</v>
       </c>
       <c r="X5" s="9"/>
@@ -2395,7 +2403,7 @@
       <c r="V6" s="8">
         <v>0.28699999999999998</v>
       </c>
-      <c r="W6" s="91">
+      <c r="W6" s="87">
         <v>0.253</v>
       </c>
       <c r="X6" s="9"/>
@@ -3771,7 +3779,7 @@
       <c r="V25" s="6">
         <v>333</v>
       </c>
-      <c r="W25" s="92">
+      <c r="W25" s="88">
         <v>238</v>
       </c>
       <c r="X25" s="6"/>
@@ -17374,19 +17382,19 @@
     </row>
     <row r="67" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B67" s="77"/>
-      <c r="C67" s="86" t="s">
+      <c r="C67" s="89" t="s">
         <v>215</v>
       </c>
-      <c r="D67" s="86"/>
-      <c r="E67" s="86"/>
-      <c r="F67" s="86"/>
-      <c r="G67" s="86"/>
-      <c r="H67" s="86"/>
-      <c r="I67" s="86"/>
-      <c r="J67" s="87"/>
+      <c r="D67" s="89"/>
+      <c r="E67" s="89"/>
+      <c r="F67" s="89"/>
+      <c r="G67" s="89"/>
+      <c r="H67" s="89"/>
+      <c r="I67" s="89"/>
+      <c r="J67" s="90"/>
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B68" s="88" t="s">
+      <c r="B68" s="91" t="s">
         <v>214</v>
       </c>
       <c r="C68" s="78"/>
@@ -17399,7 +17407,7 @@
       <c r="J68" s="79"/>
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B69" s="88"/>
+      <c r="B69" s="91"/>
       <c r="C69" s="80"/>
       <c r="D69" s="81"/>
       <c r="E69" s="81"/>
@@ -17410,7 +17418,7 @@
       <c r="J69" s="81"/>
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B70" s="88"/>
+      <c r="B70" s="91"/>
       <c r="C70" s="80"/>
       <c r="D70" s="81"/>
       <c r="E70" s="81"/>
@@ -17421,7 +17429,7 @@
       <c r="J70" s="81"/>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B71" s="88"/>
+      <c r="B71" s="91"/>
       <c r="C71" s="80"/>
       <c r="D71" s="81"/>
       <c r="E71" s="81"/>
@@ -17432,7 +17440,7 @@
       <c r="J71" s="81"/>
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B72" s="88"/>
+      <c r="B72" s="91"/>
       <c r="C72" s="80"/>
       <c r="D72" s="81"/>
       <c r="E72" s="81"/>
@@ -17443,7 +17451,7 @@
       <c r="J72" s="81"/>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B73" s="88"/>
+      <c r="B73" s="91"/>
       <c r="C73" s="80"/>
       <c r="D73" s="81"/>
       <c r="E73" s="81"/>
@@ -17454,7 +17462,7 @@
       <c r="J73" s="81"/>
     </row>
     <row r="74" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B74" s="88"/>
+      <c r="B74" s="91"/>
       <c r="C74" s="80"/>
       <c r="D74" s="81"/>
       <c r="E74" s="81"/>
@@ -17465,7 +17473,7 @@
       <c r="J74" s="81"/>
     </row>
     <row r="75" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B75" s="89"/>
+      <c r="B75" s="92"/>
       <c r="C75" s="80"/>
       <c r="D75" s="81"/>
       <c r="E75" s="81"/>
